--- a/labeled_dataset.xlsx
+++ b/labeled_dataset.xlsx
@@ -521,41 +521,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>http://app-sushiswaps.net/</t>
+          <t>https://shopeejkt4782.blogspot.com/</t>
         </is>
       </c>
       <c r="B2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -567,17 +567,17 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>49</v>
+        <v>9541</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>9540</v>
+        <v>9541</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -719,41 +719,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://shopeejkt4782.blogspot.com/</t>
+          <t>http://app-sushiswaps.net/</t>
         </is>
       </c>
       <c r="B5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -765,17 +765,17 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>9540</v>
+        <v>49</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -785,26 +785,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://teamyk.com/</t>
+          <t>http://viewdetail1109yvsaxq.growthcrm-platf.com/public/</t>
         </is>
       </c>
       <c r="B6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
@@ -816,32 +816,32 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
         <v>6</v>
       </c>
-      <c r="L6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
+          <t>'+1 no HTTPS; +2 gibberish subdomain; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -851,17 +851,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>http://xfinityconnectupgrade.weebly.com/</t>
+          <t>https://teamyk.com/</t>
         </is>
       </c>
       <c r="B7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -870,22 +870,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>3.78</v>
+        <v>2.58</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -897,17 +897,17 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7474</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -917,20 +917,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>http://viewdetail1109yvsaxq.growthcrm-platf.com/public/</t>
+          <t>http://xfinityconnectupgrade.weebly.com/</t>
         </is>
       </c>
       <c r="B8" t="b">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -942,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -963,17 +963,17 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>7474</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 gibberish subdomain; +3 domain under 30 days old</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -983,20 +983,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://sub.parsnetsecure.ir/</t>
+          <t>https://wordpress-214953-0.cloudclusters.net/FCKundenservice/ZXJ2aWc2VS/sbbclient/</t>
         </is>
       </c>
       <c r="B9" t="b">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>3.84</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1028,16 +1028,18 @@
       <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>2845</v>
+      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1047,20 +1049,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://1url.at/www/robloxcom-users-2742864312473-profile</t>
+          <t>https://safe-browsing-hub.com/click?key=4454a8862e69440f92556bd101acd0f6</t>
         </is>
       </c>
       <c r="B10" t="b">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1078,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>3.73</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1092,16 +1094,18 @@
       <c r="O10" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1177,20 +1181,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://jipacsja.vercel.app/</t>
+          <t>https://1url.at/www/robloxcom-users-2742864312473-profile</t>
         </is>
       </c>
       <c r="B12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1202,16 +1206,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1227,11 +1231,11 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>'+2 free hosting</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1241,17 +1245,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://seraji.at/.tmb/index(1).html</t>
+          <t>https://sub.parsnetsecure.ir/</t>
         </is>
       </c>
       <c r="B13" t="b">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1269,13 +1273,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1291,11 +1295,11 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1305,23 +1309,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://golden-pollen-74.tinidrop.app/?eta=ororsys@d7dbc5249851bc818ec6bda4567ca2b558f5.net</t>
+          <t>https://jipacsja.vercel.app/</t>
         </is>
       </c>
       <c r="B14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -1330,16 +1334,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1355,11 +1359,11 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>'+2 '@' in URL; +1 page unreachable (unverifiable); +2 gibberish subdomain; +1 no registration record found</t>
+          <t>'+2 free hosting</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1369,14 +1373,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.robiox.com.py/games/121864768012064/NOW-Fish-It?privateServerLinkCode=224860681404118230647368451253</t>
+          <t>https://golden-pollen-74.tinidrop.app/?eta=ororsys@d7dbc5249851bc818ec6bda4567ca2b558f5.net</t>
         </is>
       </c>
       <c r="B15" t="b">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -1385,7 +1389,7 @@
         <v>2</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -1400,10 +1404,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>3.2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1419,11 +1423,11 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+2 '@' in URL; +1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1433,20 +1437,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://wordpress-214953-0.cloudclusters.net/FCKundenservice/ZXJ2aWc2VS/sbbclient/</t>
+          <t>https://trezr-io-cloud-sso.typedream.app/</t>
         </is>
       </c>
       <c r="B16" t="b">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -1458,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1467,7 +1471,7 @@
         <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1478,18 +1482,16 @@
       <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="n">
-        <v>2845</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -1499,20 +1501,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://trezr-io-cloud-sso.typedream.app/</t>
+          <t>https://www.robiox.com.py/games/121864768012064/NOW-Fish-It?privateServerLinkCode=224860681404118230647368451253</t>
         </is>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -1530,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>3.42</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1549,11 +1551,11 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -1563,17 +1565,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://safe-browsing-hub.com/click?key=4454a8862e69440f92556bd101acd0f6</t>
+          <t>http://mtn-clone-two.vercel.app/</t>
         </is>
       </c>
       <c r="B18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1582,22 +1584,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>3.73</v>
+        <v>3.09</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1608,18 +1610,16 @@
       <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -1629,41 +1629,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>http://mtn-clone-two.vercel.app/</t>
+          <t>https://seraji.at/.tmb/index(1).html</t>
         </is>
       </c>
       <c r="B19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>3.09</v>
+        <v>2.58</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1679,11 +1679,11 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -1743,11 +1743,11 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +1 no registration record found</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -1823,17 +1823,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>http://app.casamarmol.com.ve/Public/home</t>
+          <t>https://conver.summitleadf.com/</t>
         </is>
       </c>
       <c r="B22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>0.92</v>
+        <v>2.58</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1868,16 +1868,18 @@
       <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -1887,17 +1889,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>http://app.casamarmol.com.ve/Public/home/next.php</t>
+          <t>http://facebookhotysexyvideos.blogspot.com/</t>
         </is>
       </c>
       <c r="B23" t="b">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1912,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L23" t="n">
-        <v>0.92</v>
+        <v>3.7</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1932,16 +1934,18 @@
       <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>9541</v>
+      </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +1 no registration record found</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -1951,17 +1955,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>http://facebookhotysexyvideos.blogspot.com/</t>
+          <t>http://vvxjpzx.clicks.mlsend.com/td/cl/eyJ2Ijoie1wiYVwiOjI2MTQ3ODQsXCJsXCI6MTk4NTcxNDY4NjE4OTkxMDMxLFwiclwiOjE5ODU3MTQ4MDMxOTAwMTc3MX0iLCJzIjoiZjE5ZGNhOWU0NDc5MjE3YSJ9/</t>
         </is>
       </c>
       <c r="B24" t="b">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1976,16 +1980,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
-        <v>3.7</v>
+        <v>2.24</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1997,17 +2001,17 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>9540</v>
+        <v>5718</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2017,41 +2021,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://meta-verified-blueticks-fb15.vercel.app/privacy-centers.html</t>
+          <t>http://app.casamarmol.com.ve/Public/home/next.php</t>
         </is>
       </c>
       <c r="B25" t="b">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>3.97</v>
+        <v>0.92</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2067,11 +2071,11 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>'+2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2081,14 +2085,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>http://www.facebookhotysexyvideos.blogspot.com/</t>
+          <t>http://app.casamarmol.com.ve/Public/home</t>
         </is>
       </c>
       <c r="B26" t="b">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -2106,16 +2110,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>3.7</v>
+        <v>0.92</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2126,18 +2130,16 @@
       <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="n">
-        <v>9540</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2147,41 +2149,41 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>http://vvxjpzx.clicks.mlsend.com/td/cl/eyJ2Ijoie1wiYVwiOjI2MTQ3ODQsXCJsXCI6MTk4NTcxNDY4NjE4OTkxMDMxLFwiclwiOjE5ODU3MTQ4MDMxOTAwMTc3MX0iLCJzIjoiZjE5ZGNhOWU0NDc5MjE3YSJ9/</t>
+          <t>https://meta-verified-blueticks-fb15.vercel.app/privacy-centers.html</t>
         </is>
       </c>
       <c r="B27" t="b">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
       <c r="G27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="L27" t="n">
-        <v>2.24</v>
+        <v>3.97</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2192,18 +2194,16 @@
       <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="n">
-        <v>5718</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS</t>
+          <t>'+2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -2213,20 +2213,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://conver.summitleadf.com/</t>
+          <t>https://goyang-shopee77.blogspot.com/</t>
         </is>
       </c>
       <c r="B28" t="b">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         <v>0</v>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>2.58</v>
+        <v>3.37</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2259,17 +2259,17 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>9541</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -2279,26 +2279,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://goyang-shopee77.blogspot.com/</t>
+          <t>http://www.facebookhotysexyvideos.blogspot.com/</t>
         </is>
       </c>
       <c r="B29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
       </c>
       <c r="G29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -2310,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L29" t="n">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>9540</v>
+        <v>9541</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -2345,26 +2345,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://gizmotide.com/3ter</t>
+          <t>http://www.cn-host-whatsapp.com.cn/</t>
         </is>
       </c>
       <c r="B30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
       </c>
       <c r="G30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="b">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>2.95</v>
+        <v>-0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
+          <t>'+1 no HTTPS; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -2461,11 +2461,11 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4937</v>
+        <v>4938</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2541,41 +2541,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>http://www.cn-host-whatsapp.com.cn/</t>
+          <t>https://sahilsingh8877.github.io/Netflix---Clone</t>
         </is>
       </c>
       <c r="B33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
       <c r="G33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L33" t="n">
-        <v>-0</v>
+        <v>3.09</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2587,17 +2587,17 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>4938</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +3 domain under 30 days old</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -2607,20 +2607,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://sahilsingh8877.github.io/Netflix---Clone</t>
+          <t>https://gizmotide.com/3ter</t>
         </is>
       </c>
       <c r="B34" t="b">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -2632,16 +2632,16 @@
         <v>0</v>
       </c>
       <c r="I34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L34" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2653,17 +2653,17 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4937</v>
+        <v>29</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -2673,41 +2673,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://zfkmasinac.com/pe/alibaba/</t>
+          <t>http://connect-xfinity-log.weebly.com/</t>
         </is>
       </c>
       <c r="B35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
       <c r="G35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L35" t="n">
-        <v>3.12</v>
+        <v>3.47</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2719,17 +2719,17 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7039</v>
+        <v>7474</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -2739,17 +2739,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>http://connect-xfinity-log.weebly.com/</t>
+          <t>https://1708dkfjxusxkxlolxxisdforxxllp1-endpoint-d9huf9bsffb3hab8.z03.azurefd.net/</t>
         </is>
       </c>
       <c r="B36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -2770,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="L36" t="n">
-        <v>3.47</v>
+        <v>4.53</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>7474</v>
+        <v>3051</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -2805,26 +2805,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://1708dkfjxusxkxlolxxisdforxxllp1-endpoint-d9huf9bsffb3hab8.z03.azurefd.net/</t>
+          <t>http://xfinityconnectemail.weebly.com/</t>
         </is>
       </c>
       <c r="B37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
       </c>
       <c r="G37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -2836,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="L37" t="n">
-        <v>4.53</v>
+        <v>3.43</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3050</v>
+        <v>7474</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -2871,17 +2871,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>http://xfinityconnectemail.weebly.com/</t>
+          <t>https://zfkmasinac.com/pe/alibaba/</t>
         </is>
       </c>
       <c r="B38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2890,22 +2890,22 @@
         <v>0</v>
       </c>
       <c r="G38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L38" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2917,17 +2917,17 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>7474</v>
+        <v>7040</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -3001,14 +3001,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://dev.epressefdex.top/app/login</t>
+          <t>https://dev.epressefdex.top/</t>
         </is>
       </c>
       <c r="B40" t="b">
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D40" t="n">
         <v>2</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
@@ -3053,11 +3053,11 @@
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +3 domain under 30 days old</t>
+          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -3067,14 +3067,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://dev.epressefdex.top/</t>
+          <t>https://dev.epressefdex.top/app/login</t>
         </is>
       </c>
       <c r="B41" t="b">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D41" t="n">
         <v>2</v>
@@ -3095,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>3</v>
@@ -3119,11 +3119,11 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>9540</v>
+        <v>9541</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -3265,20 +3265,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://blockbook-vtc-1.nodes.zelcore.io/</t>
+          <t>https://connectxfinitysignin.weebly.com/</t>
         </is>
       </c>
       <c r="B44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -3290,19 +3290,19 @@
         <v>0</v>
       </c>
       <c r="I44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L44" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -3311,17 +3311,17 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2930</v>
+        <v>7474</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>'+2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -3331,20 +3331,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://connectxfinitysignin.weebly.com/</t>
+          <t>https://blockbook-vtc-1.nodes.zelcore.io/</t>
         </is>
       </c>
       <c r="B45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3356,19 +3356,19 @@
         <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L45" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -3377,17 +3377,17 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>7474</v>
+        <v>2931</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -3442,16 +3442,18 @@
       <c r="O46" t="b">
         <v>0</v>
       </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>194</v>
+      </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 gibberish subdomain; +1 no registration record found</t>
+          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -3507,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>9540</v>
+        <v>9541</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
@@ -3573,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>9540</v>
+        <v>9541</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -3643,11 +3645,11 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -3657,41 +3659,41 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>http://staging.d21fuecwzi5di9.amplifyapp.com/</t>
+          <t>https://www.roblox.com.pt/games/79402242188809/Baddie-Tag?privateServerLinkCode=85761403516745353131454885790386</t>
         </is>
       </c>
       <c r="B50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
       <c r="G50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>4.06</v>
+        <v>-0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3703,17 +3705,17 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3072</v>
+        <v>63</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -3769,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -3789,17 +3791,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>http://mintleaf.pages.dev/</t>
+          <t>http://staging.d21fuecwzi5di9.amplifyapp.com/</t>
         </is>
       </c>
       <c r="B52" t="b">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -3820,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L52" t="n">
-        <v>3</v>
+        <v>4.06</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -3834,16 +3836,18 @@
       <c r="O52" t="b">
         <v>0</v>
       </c>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>3072</v>
+      </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -3853,20 +3857,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>http://sp30ct-korex-biz-zemur-nadix.pages.dev/</t>
+          <t>http://mintleaf.pages.dev/</t>
         </is>
       </c>
       <c r="B53" t="b">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D53" t="n">
         <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -3884,10 +3888,10 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
-        <v>4.16</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3898,16 +3902,18 @@
       <c r="O53" t="b">
         <v>0</v>
       </c>
-      <c r="P53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>2203</v>
+      </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -3917,41 +3923,41 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.roblox.com.pt/games/79402242188809/Baddie-Tag?privateServerLinkCode=85761403516745353131454885790386</t>
+          <t>http://sp30ct-korex-biz-zemur-nadix.pages.dev/</t>
         </is>
       </c>
       <c r="B54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
       </c>
       <c r="G54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
       </c>
       <c r="I54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L54" t="n">
-        <v>-0</v>
+        <v>4.16</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3963,17 +3969,17 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>63</v>
+        <v>2203</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable)</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -4033,11 +4039,11 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 gibberish subdomain; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -4097,11 +4103,11 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -4177,17 +4183,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://facebokksecurity.blogspot.com/?m=1</t>
+          <t>https://usc1.contabostorage.com/033941d03d9c489184023a21e9a838f6:jlk/indexngp.html</t>
         </is>
       </c>
       <c r="B58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -4202,16 +4208,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L58" t="n">
-        <v>3.62</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -4223,19 +4229,15 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>9540</v>
+        <v>1663</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>5</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="n">
         <v>1</v>
       </c>
@@ -4243,14 +4245,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://coinbaise.vercel.app/assets</t>
+          <t>https://facebokksecurity.blogspot.com/?m=1</t>
         </is>
       </c>
       <c r="B59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D59" t="n">
         <v>2</v>
@@ -4274,10 +4276,10 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L59" t="n">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -4288,16 +4290,18 @@
       <c r="O59" t="b">
         <v>0</v>
       </c>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>9541</v>
+      </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>'+2 free hosting</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -4307,14 +4311,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://usc1.contabostorage.com/033941d03d9c489184023a21e9a838f6:jlk/indexngp.html</t>
+          <t>https://www.facebokksecurity.blogspot.com/?m=1</t>
         </is>
       </c>
       <c r="B60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="D60" t="n">
         <v>3</v>
@@ -4332,16 +4336,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>3.62</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -4353,15 +4357,19 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1663</v>
+        <v>9541</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+        </is>
+      </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
@@ -4369,17 +4377,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.facebokksecurity.blogspot.com/?m=1</t>
+          <t>https://coinbaise.vercel.app/assets</t>
         </is>
       </c>
       <c r="B61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -4400,10 +4408,10 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L61" t="n">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -4414,18 +4422,16 @@
       <c r="O61" t="b">
         <v>0</v>
       </c>
-      <c r="P61" t="n">
-        <v>9540</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+2 free hosting</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -4480,11 +4486,9 @@
       <c r="O62" t="b">
         <v>0</v>
       </c>
-      <c r="P62" t="n">
-        <v>3050</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>5</v>
@@ -4546,11 +4550,9 @@
       <c r="O63" t="b">
         <v>0</v>
       </c>
-      <c r="P63" t="n">
-        <v>2203</v>
-      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>5</v>
@@ -4567,20 +4569,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>http://www.shopbidaithanroblox.com/</t>
+          <t>http://ze-em.netlify.app/</t>
         </is>
       </c>
       <c r="B64" t="b">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -4592,16 +4594,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L64" t="n">
-        <v>-0</v>
+        <v>1.92</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -4612,18 +4614,16 @@
       <c r="O64" t="b">
         <v>0</v>
       </c>
-      <c r="P64" t="n">
-        <v>588</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS</t>
+          <t>'+1 no HTTPS; +2 free hosting</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -4633,20 +4633,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>http://ze-em.netlify.app/</t>
+          <t>http://eua2worldinfo.vercel.app/</t>
         </is>
       </c>
       <c r="B65" t="b">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D65" t="n">
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -4664,32 +4664,30 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
+        <v>13</v>
+      </c>
+      <c r="L65" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
         <v>5</v>
       </c>
-      <c r="L65" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="b">
-        <v>0</v>
-      </c>
-      <c r="O65" t="b">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>3050</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>3</v>
-      </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -4699,14 +4697,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>http://eua2worldinfo.vercel.app/</t>
+          <t>http://www.shopbidaithanroblox.com/</t>
         </is>
       </c>
       <c r="B66" t="b">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -4724,16 +4722,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L66" t="n">
-        <v>3.55</v>
+        <v>-0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -4745,17 +4743,17 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2421</v>
+        <v>589</v>
       </c>
       <c r="Q66" t="n">
         <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -4810,11 +4808,9 @@
       <c r="O67" t="b">
         <v>0</v>
       </c>
-      <c r="P67" t="n">
-        <v>2421</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>4</v>
@@ -4876,11 +4872,9 @@
       <c r="O68" t="b">
         <v>0</v>
       </c>
-      <c r="P68" t="n">
-        <v>2421</v>
-      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>4</v>
@@ -4947,11 +4941,11 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -5011,11 +5005,11 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -5155,14 +5149,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>http://s.wpfc.ml/p9/mg/</t>
+          <t>https://loginservice.cloud/E.Gl_MZ3n5KmFWyRSUZw?/g/personal/hakim_ask4key_com/ETvMuE2HPLpPgskR0RfHG0sBk3kf43GwtcnE26u0vW301g?e=rF2mfd</t>
         </is>
       </c>
       <c r="B73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="D73" t="n">
         <v>2</v>
@@ -5174,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
@@ -5183,13 +5177,13 @@
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L73" t="n">
-        <v>-0</v>
+        <v>3.25</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -5200,16 +5194,18 @@
       <c r="O73" t="b">
         <v>0</v>
       </c>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>531</v>
+      </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -5219,14 +5215,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://loginservice.cloud/E.Gl_MZ3n5KmFWyRSUZw?/g/personal/hakim_ask4key_com/ETvMuE2HPLpPgskR0RfHG0sBk3kf43GwtcnE26u0vW301g?e=rF2mfd</t>
+          <t>http://s.wpfc.ml/p9/mg/</t>
         </is>
       </c>
       <c r="B74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
@@ -5238,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -5247,13 +5243,13 @@
         <v>0</v>
       </c>
       <c r="J74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>3.25</v>
+        <v>-0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -5264,18 +5260,16 @@
       <c r="O74" t="b">
         <v>0</v>
       </c>
-      <c r="P74" t="n">
-        <v>531</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -5395,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
@@ -5477,41 +5471,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>http://comcastvm.weebly.com/</t>
+          <t>https://fls-a2bb25f6-3245-4fcb-a849-103ffc861cc6.laravel.cloud/dmain.html</t>
         </is>
       </c>
       <c r="B78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
       </c>
       <c r="G78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
       </c>
       <c r="I78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="b">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="L78" t="n">
-        <v>2.73</v>
+        <v>3.82</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -5523,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>7474</v>
+        <v>3363</v>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
@@ -5533,7 +5527,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -5543,20 +5537,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>http://comcastseettings.weebly.com/</t>
+          <t>http://check-maps.us/7Ia</t>
         </is>
       </c>
       <c r="B79" t="b">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -5568,16 +5562,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -5589,17 +5583,17 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>7474</v>
+        <v>351</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -5609,41 +5603,41 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://fls-a2bb25f6-3245-4fcb-a849-103ffc861cc6.laravel.cloud/dmain.html</t>
+          <t>http://comcastvm.weebly.com/</t>
         </is>
       </c>
       <c r="B80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
       </c>
       <c r="G80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="L80" t="n">
-        <v>3.82</v>
+        <v>2.73</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -5655,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>3363</v>
+        <v>7474</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -5665,7 +5659,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -5675,20 +5669,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>http://xinfinitysignin.weebly.com/</t>
+          <t>http://check-maps.us/zrO</t>
         </is>
       </c>
       <c r="B81" t="b">
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -5700,16 +5694,16 @@
         <v>0</v>
       </c>
       <c r="I81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -5721,17 +5715,17 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>7474</v>
+        <v>351</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 suspicious keyword in URL; +2 free hosting</t>
+          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -5741,14 +5735,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://au.evergreenfin.ltd/</t>
+          <t>http://xinfinitysignin.weebly.com/</t>
         </is>
       </c>
       <c r="B82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D82" t="n">
         <v>2</v>
@@ -5760,22 +5754,22 @@
         <v>0</v>
       </c>
       <c r="G82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
       </c>
       <c r="I82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -5786,16 +5780,18 @@
       <c r="O82" t="b">
         <v>0</v>
       </c>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>7474</v>
+      </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 no HTTPS; +2 suspicious keyword in URL; +2 free hosting</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -5805,14 +5801,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>http://xinfinitycommunication.weebly.com/</t>
+          <t>http://comcastseettings.weebly.com/</t>
         </is>
       </c>
       <c r="B83" t="b">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D83" t="n">
         <v>2</v>
@@ -5836,10 +5832,10 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L83" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -5871,20 +5867,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>http://check-maps.us/zrO</t>
+          <t>http://xinfinitycommunication.weebly.com/</t>
         </is>
       </c>
       <c r="B84" t="b">
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -5896,16 +5892,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="L84" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -5917,17 +5913,17 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>351</v>
+        <v>7474</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -5937,26 +5933,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>http://check-maps.us/7Ia</t>
+          <t>https://au.evergreenfin.ltd/</t>
         </is>
       </c>
       <c r="B85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
       </c>
       <c r="G85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
@@ -5968,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>3.12</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -5982,18 +5978,16 @@
       <c r="O85" t="b">
         <v>0</v>
       </c>
-      <c r="P85" t="n">
-        <v>351</v>
-      </c>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -6003,20 +5997,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://auction.evergreenfin.ltd/</t>
+          <t>https://listivo.de/offincial-mircosftbilluiling/cc.php</t>
         </is>
       </c>
       <c r="B86" t="b">
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -6037,7 +6031,7 @@
         <v>7</v>
       </c>
       <c r="L86" t="n">
-        <v>2.81</v>
+        <v>2.52</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -6053,11 +6047,11 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -6067,20 +6061,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://listivo.de/offincial-mircosftbilluiling/cc.php</t>
+          <t>https://auction.evergreenfin.ltd/</t>
         </is>
       </c>
       <c r="B87" t="b">
         <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -6101,7 +6095,7 @@
         <v>7</v>
       </c>
       <c r="L87" t="n">
-        <v>2.52</v>
+        <v>2.81</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -6117,11 +6111,11 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -6131,20 +6125,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://wordpress-214953-0.cloudclusters.net/Kundenservice/GVuc2Vyd/lifWebSignIn&amp;flowE/</t>
+          <t>https://www.temiydcbnjt.vercel.app/</t>
         </is>
       </c>
       <c r="B88" t="b">
         <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -6159,13 +6153,13 @@
         <v>1</v>
       </c>
       <c r="J88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L88" t="n">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -6176,18 +6170,16 @@
       <c r="O88" t="b">
         <v>0</v>
       </c>
-      <c r="P88" t="n">
-        <v>2845</v>
-      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -6197,20 +6189,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.temiydcbnjt.vercel.app/</t>
+          <t>https://wordpress-214953-0.cloudclusters.net/Kundenservice/GVuc2Vyd/lifWebSignIn&amp;flowE/</t>
         </is>
       </c>
       <c r="B89" t="b">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -6225,13 +6217,13 @@
         <v>1</v>
       </c>
       <c r="J89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L89" t="n">
-        <v>3.28</v>
+        <v>3.84</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -6242,16 +6234,18 @@
       <c r="O89" t="b">
         <v>0</v>
       </c>
-      <c r="P89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>2845</v>
+      </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -6307,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -6391,20 +6385,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://instagramlogin99.blogspot.com/</t>
+          <t>https://www.auth-portal.sbs/</t>
         </is>
       </c>
       <c r="B92" t="b">
         <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D92" t="n">
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -6416,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L92" t="n">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -6437,17 +6431,17 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>9540</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -6503,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
@@ -6653,20 +6647,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.auth-portal.sbs/</t>
+          <t>https://instagramlogin99.blogspot.com/</t>
         </is>
       </c>
       <c r="B96" t="b">
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -6678,16 +6672,16 @@
         <v>0</v>
       </c>
       <c r="I96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L96" t="n">
-        <v>-0</v>
+        <v>3.38</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -6699,17 +6693,17 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>9541</v>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -6765,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>4937</v>
+        <v>4938</v>
       </c>
       <c r="Q97" t="n">
         <v>1</v>
@@ -6785,14 +6779,14 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://adfs.evergreenfin.ltd/</t>
+          <t>https://s0l1c1tud56.freepage.cc/</t>
         </is>
       </c>
       <c r="B98" t="b">
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
@@ -6816,10 +6810,10 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -6830,16 +6824,18 @@
       <c r="O98" t="b">
         <v>0</v>
       </c>
-      <c r="P98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>110</v>
+      </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -6849,14 +6845,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://s0l1c1tud56.freepage.cc/</t>
+          <t>https://adfs.evergreenfin.ltd/</t>
         </is>
       </c>
       <c r="B99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D99" t="n">
         <v>2</v>
@@ -6880,10 +6876,10 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L99" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -6894,18 +6890,16 @@
       <c r="O99" t="b">
         <v>0</v>
       </c>
-      <c r="P99" t="n">
-        <v>110</v>
-      </c>
+      <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>'+2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -6981,20 +6975,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://site-ma-ga-zine-luiza.com/checkout</t>
+          <t>https://simo290.github.io/instagram</t>
         </is>
       </c>
       <c r="B101" t="b">
         <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -7006,16 +7000,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="b">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="L101" t="n">
-        <v>3.37</v>
+        <v>2.81</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -7027,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>57</v>
+        <v>4938</v>
       </c>
       <c r="Q101" t="n">
         <v>1</v>
@@ -7037,7 +7031,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -7047,20 +7041,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://simo290.github.io/instagram</t>
+          <t>https://install-mew-documents.icu/</t>
         </is>
       </c>
       <c r="B102" t="b">
         <v>0</v>
       </c>
       <c r="C102" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102" t="b">
         <v>0</v>
@@ -7072,16 +7066,16 @@
         <v>0</v>
       </c>
       <c r="I102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L102" t="n">
-        <v>2.81</v>
+        <v>3.73</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -7093,17 +7087,17 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>4937</v>
+        <v>3</v>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -7113,20 +7107,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>http://ma1-dachf5b7cuancndx.z02.azurefd.net/</t>
+          <t>http://sp30ct-zunik-biz-murev-qavel.pages.dev/</t>
         </is>
       </c>
       <c r="B103" t="b">
         <v>1</v>
       </c>
       <c r="C103" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F103" t="b">
         <v>0</v>
@@ -7144,10 +7138,10 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L103" t="n">
-        <v>4.02</v>
+        <v>4.16</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -7158,11 +7152,9 @@
       <c r="O103" t="b">
         <v>0</v>
       </c>
-      <c r="P103" t="n">
-        <v>3050</v>
-      </c>
+      <c r="P103" t="inlineStr"/>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>5</v>
@@ -7179,20 +7171,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>http://sp30ct-zunik-biz-murev-qavel.pages.dev/</t>
+          <t>http://ma1-dachf5b7cuancndx.z02.azurefd.net/</t>
         </is>
       </c>
       <c r="B104" t="b">
         <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F104" t="b">
         <v>0</v>
@@ -7210,10 +7202,10 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L104" t="n">
-        <v>4.16</v>
+        <v>4.02</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -7224,9 +7216,11 @@
       <c r="O104" t="b">
         <v>0</v>
       </c>
-      <c r="P104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>3051</v>
+      </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
         <v>5</v>
@@ -7243,20 +7237,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://verifiedbadge-glow.vercel.app/privacy-centers.html</t>
+          <t>https://maashardaexpress.com/sign-in-immoweltchallengestate-a77aA44a35a44yNDA44adA335A434s443Qaa4aaaa21hdXRoa455A35fvvA34dsad442c1d5M3RFTkRlAA1ZTaaAA24aAsvvaWTZIEAad3xtAA55/index.htm</t>
         </is>
       </c>
       <c r="B105" t="b">
         <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" t="b">
         <v>0</v>
@@ -7268,38 +7262,36 @@
         <v>0</v>
       </c>
       <c r="I105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L105" t="n">
-        <v>3.57</v>
+        <v>2.95</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="b">
         <v>0</v>
       </c>
-      <c r="P105" t="inlineStr"/>
+      <c r="P105" t="n">
+        <v>1768</v>
+      </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>4</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>'+2 free hosting; +2 gibberish subdomain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr"/>
       <c r="T105" t="n">
         <v>1</v>
       </c>
@@ -7352,16 +7344,18 @@
       <c r="O106" t="b">
         <v>0</v>
       </c>
-      <c r="P106" t="inlineStr"/>
+      <c r="P106" t="n">
+        <v>2775</v>
+      </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +1 no registration record found</t>
+          <t>'+1 no HTTPS</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -7371,20 +7365,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://3bkevent.de.cool/index-8576.html</t>
+          <t>https://verifiedbadge-glow.vercel.app/privacy-centers.html</t>
         </is>
       </c>
       <c r="B107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D107" t="n">
         <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="b">
         <v>0</v>
@@ -7396,16 +7390,16 @@
         <v>0</v>
       </c>
       <c r="I107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" t="b">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L107" t="n">
-        <v>2.75</v>
+        <v>3.57</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -7416,16 +7410,18 @@
       <c r="O107" t="b">
         <v>0</v>
       </c>
-      <c r="P107" t="inlineStr"/>
+      <c r="P107" t="n">
+        <v>2421</v>
+      </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -7435,63 +7431,63 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://maashardaexpress.com/sign-in-immoweltchallengestate-a77aA44a35a44yNDA44adA335A434s443Qaa4aaaa21hdXRoa455A35fvvA34dsad442c1d5M3RFTkRlAA1ZTaaAA24aAsvvaWTZIEAad3xtAA55/index.htm</t>
+          <t>http://xfinitymailid.weebly.com/</t>
         </is>
       </c>
       <c r="B108" t="b">
         <v>1</v>
       </c>
       <c r="C108" t="n">
-        <v>182</v>
+        <v>32</v>
       </c>
       <c r="D108" t="n">
         <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F108" t="b">
         <v>0</v>
       </c>
       <c r="G108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" t="b">
         <v>0</v>
       </c>
       <c r="I108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" t="b">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L108" t="n">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="M108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="b">
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1768</v>
+        <v>7474</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>'+1 password field present</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -7567,41 +7563,41 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>http://xfinitymailid.weebly.com/</t>
+          <t>https://3bkevent.de.cool/index-8576.html</t>
         </is>
       </c>
       <c r="B110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="b">
         <v>0</v>
       </c>
       <c r="G110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
       </c>
       <c r="I110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" t="b">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L110" t="n">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -7613,17 +7609,17 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>7474</v>
+        <v>3861</v>
       </c>
       <c r="Q110" t="n">
         <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -7699,41 +7695,41 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://install-mew-documents.icu/</t>
+          <t>http://highspotmints072.netlify.app/</t>
         </is>
       </c>
       <c r="B112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" t="b">
         <v>0</v>
       </c>
       <c r="G112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
       </c>
       <c r="I112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="b">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L112" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -7744,18 +7740,16 @@
       <c r="O112" t="b">
         <v>0</v>
       </c>
-      <c r="P112" t="n">
-        <v>2</v>
-      </c>
+      <c r="P112" t="inlineStr"/>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -7765,14 +7759,14 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>http://highspotmints072.netlify.app/</t>
+          <t>https://linkchainsfix.vercel.app/</t>
         </is>
       </c>
       <c r="B113" t="b">
         <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -7784,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
@@ -7796,13 +7790,13 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L113" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
@@ -7811,17 +7805,17 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>3050</v>
+        <v>2421</v>
       </c>
       <c r="Q113" t="n">
         <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -7831,14 +7825,14 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://linkchainsfix.vercel.app/</t>
+          <t>https://insta1login.github.io/Reel</t>
         </is>
       </c>
       <c r="B114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D114" t="n">
         <v>2</v>
@@ -7859,16 +7853,16 @@
         <v>1</v>
       </c>
       <c r="J114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L114" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="b">
         <v>0</v>
@@ -7876,16 +7870,18 @@
       <c r="O114" t="b">
         <v>0</v>
       </c>
-      <c r="P114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>4938</v>
+      </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>'+2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -7895,14 +7891,14 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://insta1login.github.io/Reel</t>
+          <t>https://chase.phntm.com/</t>
         </is>
       </c>
       <c r="B115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D115" t="n">
         <v>2</v>
@@ -7920,16 +7916,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L115" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -7941,19 +7937,15 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>4937</v>
+        <v>6541</v>
       </c>
       <c r="Q115" t="n">
         <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>7</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable); +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr"/>
       <c r="T115" t="n">
         <v>1</v>
       </c>
@@ -8025,61 +8017,63 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://chase.phntm.com/</t>
+          <t>http://2r3k7-opu-d5z0-9x90k-08-09-2026-hh.pages.dev/</t>
         </is>
       </c>
       <c r="B117" t="b">
         <v>1</v>
       </c>
       <c r="C117" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D117" t="n">
         <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F117" t="b">
         <v>0</v>
       </c>
       <c r="G117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
       </c>
       <c r="I117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" t="b">
         <v>0</v>
       </c>
       <c r="K117" t="n">
+        <v>34</v>
+      </c>
+      <c r="L117" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="b">
+        <v>0</v>
+      </c>
+      <c r="O117" t="b">
+        <v>0</v>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
         <v>5</v>
       </c>
-      <c r="L117" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="b">
-        <v>0</v>
-      </c>
-      <c r="O117" t="b">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>6541</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+        </is>
+      </c>
       <c r="T117" t="n">
         <v>1</v>
       </c>
@@ -8087,41 +8081,41 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>http://2r3k7-opu-d5z0-9x90k-08-09-2026-hh.pages.dev/</t>
+          <t>https://attzxs.square.site/</t>
         </is>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F118" t="b">
         <v>0</v>
       </c>
       <c r="G118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
       </c>
       <c r="I118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="b">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="L118" t="n">
-        <v>3.77</v>
+        <v>2.25</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
@@ -8132,16 +8126,18 @@
       <c r="O118" t="b">
         <v>0</v>
       </c>
-      <c r="P118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>2778</v>
+      </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -8151,17 +8147,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://attzxs.square.site/</t>
+          <t>http://www.uryrhtnttt555.weebly.com/</t>
         </is>
       </c>
       <c r="B119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -8170,22 +8166,22 @@
         <v>0</v>
       </c>
       <c r="G119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
       </c>
       <c r="I119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" t="b">
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L119" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="M119" t="n">
         <v>0</v>
@@ -8197,17 +8193,17 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>2778</v>
+        <v>7474</v>
       </c>
       <c r="Q119" t="n">
         <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable)</t>
+          <t>'+1 no HTTPS; +2 free hosting</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -8217,26 +8213,26 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>http://www.uryrhtnttt555.weebly.com/</t>
+          <t>https://www.meta-verified-blueticks-fb15.vercel.app/</t>
         </is>
       </c>
       <c r="B120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D120" t="n">
         <v>3</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F120" t="b">
         <v>0</v>
       </c>
       <c r="G120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="b">
         <v>0</v>
@@ -8248,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="L120" t="n">
-        <v>2.57</v>
+        <v>3.97</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -8262,18 +8258,16 @@
       <c r="O120" t="b">
         <v>0</v>
       </c>
-      <c r="P120" t="n">
-        <v>7474</v>
-      </c>
+      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -8283,20 +8277,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.meta-verified-blueticks-fb15.vercel.app/</t>
+          <t>https://www.facebook-fields-validation-card-expand-logic.vercel.app/</t>
         </is>
       </c>
       <c r="B121" t="b">
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D121" t="n">
         <v>3</v>
       </c>
       <c r="E121" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F121" t="b">
         <v>0</v>
@@ -8314,7 +8308,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L121" t="n">
         <v>3.97</v>
@@ -8328,11 +8322,9 @@
       <c r="O121" t="b">
         <v>0</v>
       </c>
-      <c r="P121" t="n">
-        <v>2421</v>
-      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>5</v>
@@ -8413,20 +8405,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.facebook-fields-validation-card-expand-logic.vercel.app/</t>
+          <t>https://xfinity-mail-id.weeblysite.com/</t>
         </is>
       </c>
       <c r="B123" t="b">
         <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F123" t="b">
         <v>0</v>
@@ -8438,16 +8430,16 @@
         <v>0</v>
       </c>
       <c r="I123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="b">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="L123" t="n">
-        <v>3.97</v>
+        <v>3.24</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -8458,16 +8450,18 @@
       <c r="O123" t="b">
         <v>0</v>
       </c>
-      <c r="P123" t="inlineStr"/>
+      <c r="P123" t="n">
+        <v>5017</v>
+      </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -8477,14 +8471,14 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://xfinity-mail-id.weeblysite.com/</t>
+          <t>https://xfinity-mail-id.weebly.com/</t>
         </is>
       </c>
       <c r="B124" t="b">
         <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -8502,7 +8496,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="b">
         <v>0</v>
@@ -8523,17 +8517,17 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>5017</v>
+        <v>7474</v>
       </c>
       <c r="Q124" t="n">
         <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -8543,41 +8537,41 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://xfinity-mail-id.weebly.com/</t>
+          <t>http://apple-icloud.azurewebsites.net/</t>
         </is>
       </c>
       <c r="B125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D125" t="n">
         <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" t="b">
         <v>0</v>
       </c>
       <c r="G125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" t="b">
         <v>0</v>
       </c>
       <c r="I125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L125" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
@@ -8589,17 +8583,17 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>7474</v>
+        <v>5347</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -8675,41 +8669,41 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>http://apple-icloud.azurewebsites.net/</t>
+          <t>https://xfinity090.weebly.com/</t>
         </is>
       </c>
       <c r="B127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D127" t="n">
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="b">
         <v>0</v>
       </c>
       <c r="G127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127" t="b">
         <v>0</v>
       </c>
       <c r="I127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="b">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L127" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -8721,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>5346</v>
+        <v>7474</v>
       </c>
       <c r="Q127" t="n">
         <v>1</v>
@@ -8731,7 +8725,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -8741,41 +8735,41 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>http://digitalonlineworld.vercel.app/</t>
+          <t>https://word.en-coda.shop/</t>
         </is>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D128" t="n">
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="b">
         <v>0</v>
       </c>
       <c r="G128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" t="b">
         <v>0</v>
       </c>
       <c r="I128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="b">
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L128" t="n">
-        <v>3.31</v>
+        <v>2</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -8786,18 +8780,16 @@
       <c r="O128" t="b">
         <v>0</v>
       </c>
-      <c r="P128" t="n">
-        <v>2421</v>
-      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -8807,26 +8799,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://xfinity090.weebly.com/</t>
+          <t>http://legdr-oi-wallt-s.pages.dev/</t>
         </is>
       </c>
       <c r="B129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D129" t="n">
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F129" t="b">
         <v>0</v>
       </c>
       <c r="G129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" t="b">
         <v>0</v>
@@ -8838,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L129" t="n">
-        <v>2.92</v>
+        <v>3.41</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -8852,18 +8844,16 @@
       <c r="O129" t="b">
         <v>0</v>
       </c>
-      <c r="P129" t="n">
-        <v>7474</v>
-      </c>
+      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -8923,11 +8913,11 @@
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -8937,41 +8927,41 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://word.en-coda.shop/</t>
+          <t>http://digitalonlineworld.vercel.app/</t>
         </is>
       </c>
       <c r="B131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D131" t="n">
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" t="b">
         <v>0</v>
       </c>
       <c r="G131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" t="b">
         <v>0</v>
       </c>
       <c r="I131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="b">
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L131" t="n">
-        <v>2</v>
+        <v>3.31</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -8987,11 +8977,11 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -9067,20 +9057,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>http://legdr-oi-wallt-s.pages.dev/</t>
+          <t>http://xfinitiuser.weebly.com/</t>
         </is>
       </c>
       <c r="B133" t="b">
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D133" t="n">
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F133" t="b">
         <v>0</v>
@@ -9098,10 +9088,10 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L133" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
@@ -9113,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>2203</v>
+        <v>7474</v>
       </c>
       <c r="Q133" t="n">
         <v>1</v>
@@ -9133,17 +9123,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>http://xfinitiuser.weebly.com/</t>
+          <t>https://imcoin.me/</t>
         </is>
       </c>
       <c r="B134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -9152,22 +9142,22 @@
         <v>0</v>
       </c>
       <c r="G134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" t="b">
         <v>0</v>
       </c>
       <c r="I134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" t="b">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L134" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -9179,17 +9169,17 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>7474</v>
+        <v>4</v>
       </c>
       <c r="Q134" t="n">
         <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -9199,14 +9189,14 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>http://xfinitymail087.weebly.com/</t>
+          <t>http://xfintyid.weebly.com/</t>
         </is>
       </c>
       <c r="B135" t="b">
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D135" t="n">
         <v>2</v>
@@ -9230,10 +9220,10 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L135" t="n">
-        <v>3.47</v>
+        <v>2.75</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -9251,11 +9241,11 @@
         <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 free hosting</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -9265,14 +9255,14 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>http://xfintyid.weebly.com/</t>
+          <t>http://xfinitymail087.weebly.com/</t>
         </is>
       </c>
       <c r="B136" t="b">
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D136" t="n">
         <v>2</v>
@@ -9296,10 +9286,10 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L136" t="n">
-        <v>2.75</v>
+        <v>3.47</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -9317,11 +9307,11 @@
         <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 free hosting</t>
+          <t>'+1 no HTTPS; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -9331,17 +9321,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://imcoin.me/</t>
+          <t>https://aad.evergreenfin.ltd/</t>
         </is>
       </c>
       <c r="B137" t="b">
         <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -9362,10 +9352,10 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L137" t="n">
-        <v>2.25</v>
+        <v>0.92</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -9376,18 +9366,16 @@
       <c r="O137" t="b">
         <v>0</v>
       </c>
-      <c r="P137" t="n">
-        <v>4</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +3 domain under 30 days old</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -9397,20 +9385,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://aad.evergreenfin.ltd/</t>
+          <t>https://rajveersolanki06.github.io/spotify-clone</t>
         </is>
       </c>
       <c r="B138" t="b">
         <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D138" t="n">
         <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="b">
         <v>0</v>
@@ -9422,16 +9410,16 @@
         <v>0</v>
       </c>
       <c r="I138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138" t="b">
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L138" t="n">
-        <v>0.92</v>
+        <v>3.62</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -9442,16 +9430,18 @@
       <c r="O138" t="b">
         <v>0</v>
       </c>
-      <c r="P138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>4938</v>
+      </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -9461,14 +9451,14 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://rajveersolanki06.github.io/spotify-clone</t>
+          <t>https://tushar7826.github.io/Netflix-Clone</t>
         </is>
       </c>
       <c r="B139" t="b">
         <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D139" t="n">
         <v>2</v>
@@ -9492,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L139" t="n">
-        <v>3.62</v>
+        <v>3.32</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -9507,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>4937</v>
+        <v>4938</v>
       </c>
       <c r="Q139" t="n">
         <v>1</v>
@@ -9589,26 +9579,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://tushar7826.github.io/Netflix-Clone</t>
+          <t>http://xfinty-email-update.weebly.com/</t>
         </is>
       </c>
       <c r="B141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D141" t="n">
         <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" t="b">
         <v>0</v>
       </c>
       <c r="G141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="b">
         <v>0</v>
@@ -9617,13 +9607,13 @@
         <v>1</v>
       </c>
       <c r="J141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L141" t="n">
-        <v>3.32</v>
+        <v>3.72</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -9635,17 +9625,17 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>4937</v>
+        <v>7474</v>
       </c>
       <c r="Q141" t="n">
         <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 no HTTPS; +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -9655,41 +9645,41 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>http://xfinty-email-update.weebly.com/</t>
+          <t>https://site-ma-ga-zine-luiza.com/checkout</t>
         </is>
       </c>
       <c r="B142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142" t="b">
         <v>0</v>
       </c>
       <c r="G142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="b">
         <v>0</v>
       </c>
       <c r="I142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L142" t="n">
-        <v>3.72</v>
+        <v>3.37</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -9701,17 +9691,17 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>7474</v>
+        <v>57</v>
       </c>
       <c r="Q142" t="n">
         <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>'+1 no HTTPS; +2 suspicious keyword in URL; +2 free hosting; +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -9851,20 +9841,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://hsd05e53837dec3946be106277583f5550.nexusqalinka2.lol/</t>
+          <t>https://css-ch.blogspot.com/</t>
         </is>
       </c>
       <c r="B145" t="b">
         <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D145" t="n">
         <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="b">
         <v>0</v>
@@ -9876,16 +9866,16 @@
         <v>0</v>
       </c>
       <c r="I145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="b">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="L145" t="n">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -9897,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>34</v>
+        <v>9541</v>
       </c>
       <c r="Q145" t="n">
         <v>1</v>
@@ -9907,7 +9897,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
+          <t>'+1 page unreachable (unverifiable); +2 free hosting</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -9917,20 +9907,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://css-ch.blogspot.com/</t>
+          <t>https://hsd05e53837dec3946be106277583f5550.nexusqalinka2.lol/</t>
         </is>
       </c>
       <c r="B146" t="b">
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D146" t="n">
         <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" t="b">
         <v>0</v>
@@ -9942,16 +9932,16 @@
         <v>0</v>
       </c>
       <c r="I146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="b">
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="L146" t="n">
-        <v>1.92</v>
+        <v>3.8</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -9963,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>9540</v>
+        <v>34</v>
       </c>
       <c r="Q146" t="n">
         <v>1</v>
@@ -9973,7 +9963,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +2 free hosting</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -9983,20 +9973,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://netflix.patelrudra.in/</t>
+          <t>https://australiangifts-xs802.ink/KxP3tN</t>
         </is>
       </c>
       <c r="B147" t="b">
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="b">
         <v>0</v>
@@ -10014,10 +10004,10 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L147" t="n">
-        <v>2.81</v>
+        <v>3.75</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -10029,17 +10019,17 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>377</v>
+        <v>5</v>
       </c>
       <c r="Q147" t="n">
         <v>1</v>
       </c>
       <c r="R147" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable)</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -10099,11 +10089,11 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable); +1 no registration record found</t>
+          <t>'+1 page unreachable (unverifiable)</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -10113,14 +10103,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.google.com</t>
+          <t>https://netflix.patelrudra.in/</t>
         </is>
       </c>
       <c r="B149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D149" t="n">
         <v>2</v>
@@ -10144,13 +10134,13 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L149" t="n">
-        <v>-0</v>
+        <v>2.81</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -10159,17 +10149,21 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>10591</v>
+        <v>378</v>
       </c>
       <c r="Q149" t="n">
         <v>1</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>'+1 page unreachable (unverifiable)</t>
+        </is>
+      </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -10237,7 +10231,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.python.org</t>
+          <t>https://www.google.com</t>
         </is>
       </c>
       <c r="B151" t="b">
@@ -10283,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>11494</v>
+        <v>10591</v>
       </c>
       <c r="Q151" t="n">
         <v>1</v>
@@ -10299,14 +10293,14 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.wikipedia.org</t>
+          <t>https://www.python.org</t>
         </is>
       </c>
       <c r="B152" t="b">
         <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D152" t="n">
         <v>2</v>
@@ -10345,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>9375</v>
+        <v>11494</v>
       </c>
       <c r="Q152" t="n">
         <v>1</v>
@@ -10361,20 +10355,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://australiangifts-xs802.ink/KxP3tN</t>
+          <t>https://www.wikipedia.org</t>
         </is>
       </c>
       <c r="B153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="b">
         <v>0</v>
@@ -10392,13 +10386,13 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="L153" t="n">
-        <v>3.75</v>
+        <v>-0</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N153" t="b">
         <v>0</v>
@@ -10407,34 +10401,30 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>5</v>
+        <v>9375</v>
       </c>
       <c r="Q153" t="n">
         <v>1</v>
       </c>
       <c r="R153" t="n">
-        <v>6</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr"/>
       <c r="T153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.github.com</t>
+          <t>https://www.apple.com</t>
         </is>
       </c>
       <c r="B154" t="b">
         <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D154" t="n">
         <v>2</v>
@@ -10464,7 +10454,7 @@
         <v>-0</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -10473,7 +10463,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>6914</v>
+        <v>14452</v>
       </c>
       <c r="Q154" t="n">
         <v>1</v>
@@ -10489,14 +10479,14 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.apple.com</t>
+          <t>https://www.github.com</t>
         </is>
       </c>
       <c r="B155" t="b">
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D155" t="n">
         <v>2</v>
@@ -10526,7 +10516,7 @@
         <v>-0</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
@@ -10535,7 +10525,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>14452</v>
+        <v>6915</v>
       </c>
       <c r="Q155" t="n">
         <v>1</v>
@@ -10783,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>8716</v>
+        <v>8717</v>
       </c>
       <c r="Q159" t="n">
         <v>1</v>
@@ -10845,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>7807</v>
+        <v>7808</v>
       </c>
       <c r="Q160" t="n">
         <v>1</v>
@@ -10985,17 +10975,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.nytimes.com</t>
+          <t>http://wareumtauschens802.ink/zR8mXb</t>
         </is>
       </c>
       <c r="B163" t="b">
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -11004,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="b">
         <v>0</v>
@@ -11016,13 +11006,13 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L163" t="n">
-        <v>-0</v>
+        <v>3.73</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
@@ -11031,30 +11021,34 @@
         <v>0</v>
       </c>
       <c r="P163" t="n">
-        <v>11927</v>
+        <v>1</v>
       </c>
       <c r="Q163" t="n">
         <v>1</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>'+1 no HTTPS; +2 gibberish subdomain; +3 domain under 30 days old</t>
+        </is>
+      </c>
       <c r="T163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.bbc.com</t>
+          <t>https://www.nytimes.com</t>
         </is>
       </c>
       <c r="B164" t="b">
         <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D164" t="n">
         <v>2</v>
@@ -11084,7 +11078,7 @@
         <v>-0</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
@@ -11093,7 +11087,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>13575</v>
+        <v>11927</v>
       </c>
       <c r="Q164" t="n">
         <v>1</v>
@@ -11109,17 +11103,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>http://wareumtauschens802.ink/zR8mXb</t>
+          <t>https://www.bbc.com</t>
         </is>
       </c>
       <c r="B165" t="b">
         <v>1</v>
       </c>
       <c r="C165" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -11128,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="b">
         <v>0</v>
@@ -11140,10 +11134,10 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L165" t="n">
-        <v>3.73</v>
+        <v>-0</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -11155,21 +11149,17 @@
         <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>1</v>
+        <v>13575</v>
       </c>
       <c r="Q165" t="n">
         <v>1</v>
       </c>
       <c r="R165" t="n">
-        <v>6</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>'+1 no HTTPS; +2 gibberish subdomain; +3 domain under 30 days old</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr"/>
       <c r="T165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -11221,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>6417</v>
+        <v>6418</v>
       </c>
       <c r="Q166" t="n">
         <v>1</v>
@@ -11237,14 +11227,14 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.ibm.com</t>
+          <t>https://www.mozilla.org</t>
         </is>
       </c>
       <c r="B167" t="b">
         <v>1</v>
       </c>
       <c r="C167" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D167" t="n">
         <v>2</v>
@@ -11274,7 +11264,7 @@
         <v>-0</v>
       </c>
       <c r="M167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -11283,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="P167" t="n">
-        <v>14789</v>
+        <v>10460</v>
       </c>
       <c r="Q167" t="n">
         <v>1</v>
@@ -11299,14 +11289,14 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org</t>
+          <t>https://www.adobe.com</t>
         </is>
       </c>
       <c r="B168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D168" t="n">
         <v>2</v>
@@ -11345,15 +11335,19 @@
         <v>0</v>
       </c>
       <c r="P168" t="n">
-        <v>10460</v>
+        <v>14546</v>
       </c>
       <c r="Q168" t="n">
         <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>'+1 page unreachable (unverifiable)</t>
+        </is>
+      </c>
       <c r="T168" t="n">
         <v>0</v>
       </c>
@@ -11361,17 +11355,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.oracle.com</t>
+          <t>https://wareumtauschens801.ink/9wKqFf</t>
         </is>
       </c>
       <c r="B169" t="b">
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -11392,10 +11386,10 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L169" t="n">
-        <v>-0</v>
+        <v>3.73</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -11407,34 +11401,34 @@
         <v>0</v>
       </c>
       <c r="P169" t="n">
-        <v>13800</v>
+        <v>1</v>
       </c>
       <c r="Q169" t="n">
         <v>1</v>
       </c>
       <c r="R169" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>'+1 page unreachable (unverifiable)</t>
+          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
         </is>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com</t>
+          <t>https://www.oracle.com</t>
         </is>
       </c>
       <c r="B170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D170" t="n">
         <v>2</v>
@@ -11473,15 +11467,19 @@
         <v>0</v>
       </c>
       <c r="P170" t="n">
-        <v>10148</v>
+        <v>13800</v>
       </c>
       <c r="Q170" t="n">
         <v>1</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>'+1 page unreachable (unverifiable)</t>
+        </is>
+      </c>
       <c r="T170" t="n">
         <v>0</v>
       </c>
@@ -11489,17 +11487,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://wareumtauschens801.ink/9wKqFf</t>
+          <t>https://www.salesforce.com</t>
         </is>
       </c>
       <c r="B171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -11520,10 +11518,10 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L171" t="n">
-        <v>3.73</v>
+        <v>-0</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -11535,21 +11533,17 @@
         <v>0</v>
       </c>
       <c r="P171" t="n">
-        <v>1</v>
+        <v>10148</v>
       </c>
       <c r="Q171" t="n">
         <v>1</v>
       </c>
       <c r="R171" t="n">
-        <v>6</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable); +2 gibberish subdomain; +3 domain under 30 days old</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S171" t="inlineStr"/>
       <c r="T171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -11617,11 +11611,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.adobe.com</t>
+          <t>https://www.slack.com</t>
         </is>
       </c>
       <c r="B173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173" t="n">
         <v>21</v>
@@ -11663,19 +11657,15 @@
         <v>0</v>
       </c>
       <c r="P173" t="n">
-        <v>14546</v>
+        <v>12381</v>
       </c>
       <c r="Q173" t="n">
         <v>1</v>
       </c>
       <c r="R173" t="n">
-        <v>1</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S173" t="inlineStr"/>
       <c r="T173" t="n">
         <v>0</v>
       </c>
@@ -11683,14 +11673,14 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.slack.com</t>
+          <t>https://www.ebay.com</t>
         </is>
       </c>
       <c r="B174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D174" t="n">
         <v>2</v>
@@ -11729,15 +11719,19 @@
         <v>0</v>
       </c>
       <c r="P174" t="n">
-        <v>12381</v>
+        <v>11364</v>
       </c>
       <c r="Q174" t="n">
         <v>1</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
-      </c>
-      <c r="S174" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>'+1 page unreachable (unverifiable)</t>
+        </is>
+      </c>
       <c r="T174" t="n">
         <v>0</v>
       </c>
@@ -11807,7 +11801,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.ebay.com</t>
+          <t>https://www.uber.com</t>
         </is>
       </c>
       <c r="B176" t="b">
@@ -11853,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="P176" t="n">
-        <v>11364</v>
+        <v>11385</v>
       </c>
       <c r="Q176" t="n">
         <v>1</v>
@@ -11873,14 +11867,14 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.airbnb.com</t>
+          <t>https://www.twitch.tv</t>
         </is>
       </c>
       <c r="B177" t="b">
         <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D177" t="n">
         <v>2</v>
@@ -11910,28 +11904,24 @@
         <v>-0</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N177" t="b">
         <v>0</v>
       </c>
       <c r="O177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P177" t="n">
-        <v>6614</v>
+        <v>6306</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
       </c>
       <c r="R177" t="n">
-        <v>3</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>'+3 form posts to another host</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S177" t="inlineStr"/>
       <c r="T177" t="n">
         <v>0</v>
       </c>
@@ -11939,14 +11929,14 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.twitch.tv</t>
+          <t>https://www.airbnb.com</t>
         </is>
       </c>
       <c r="B178" t="b">
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D178" t="n">
         <v>2</v>
@@ -11976,24 +11966,28 @@
         <v>-0</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N178" t="b">
         <v>0</v>
       </c>
       <c r="O178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P178" t="n">
-        <v>6306</v>
+        <v>6614</v>
       </c>
       <c r="Q178" t="n">
         <v>1</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
-      </c>
-      <c r="S178" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>'+1 form posts to another host</t>
+        </is>
+      </c>
       <c r="T178" t="n">
         <v>0</v>
       </c>
@@ -12001,14 +11995,14 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.uber.com</t>
+          <t>https://www.chase.com</t>
         </is>
       </c>
       <c r="B179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
@@ -12038,28 +12032,24 @@
         <v>-0</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O179" t="b">
         <v>0</v>
       </c>
       <c r="P179" t="n">
-        <v>11385</v>
+        <v>11296</v>
       </c>
       <c r="Q179" t="n">
         <v>1</v>
       </c>
       <c r="R179" t="n">
-        <v>1</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S179" t="inlineStr"/>
       <c r="T179" t="n">
         <v>0</v>
       </c>
@@ -12067,14 +12057,14 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.chase.com</t>
+          <t>https://www.walmart.com</t>
         </is>
       </c>
       <c r="B180" t="b">
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D180" t="n">
         <v>2</v>
@@ -12107,25 +12097,21 @@
         <v>1</v>
       </c>
       <c r="N180" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O180" t="b">
         <v>0</v>
       </c>
       <c r="P180" t="n">
-        <v>11296</v>
+        <v>11526</v>
       </c>
       <c r="Q180" t="n">
         <v>1</v>
       </c>
       <c r="R180" t="n">
-        <v>1</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>'+1 password field present</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S180" t="inlineStr"/>
       <c r="T180" t="n">
         <v>0</v>
       </c>
@@ -12133,14 +12119,14 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.target.com</t>
+          <t>https://www.bankofamerica.com</t>
         </is>
       </c>
       <c r="B181" t="b">
         <v>1</v>
       </c>
       <c r="C181" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D181" t="n">
         <v>2</v>
@@ -12170,7 +12156,7 @@
         <v>-0</v>
       </c>
       <c r="M181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N181" t="b">
         <v>0</v>
@@ -12179,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="P181" t="n">
-        <v>10847</v>
+        <v>10122</v>
       </c>
       <c r="Q181" t="n">
         <v>1</v>
@@ -12195,14 +12181,14 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.wellsfargo.com</t>
+          <t>https://www.instagram.com</t>
         </is>
       </c>
       <c r="B182" t="b">
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D182" t="n">
         <v>2</v>
@@ -12232,28 +12218,24 @@
         <v>-0</v>
       </c>
       <c r="M182" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P182" t="n">
-        <v>12192</v>
+        <v>8137</v>
       </c>
       <c r="Q182" t="n">
         <v>1</v>
       </c>
       <c r="R182" t="n">
-        <v>6</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>'+3 form posts to another host; +1 password field present; +2 password field + external form</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S182" t="inlineStr"/>
       <c r="T182" t="n">
         <v>0</v>
       </c>
@@ -12261,14 +12243,14 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.instagram.com</t>
+          <t>https://www.stackoverflow.com</t>
         </is>
       </c>
       <c r="B183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D183" t="n">
         <v>2</v>
@@ -12307,15 +12289,19 @@
         <v>0</v>
       </c>
       <c r="P183" t="n">
-        <v>8137</v>
+        <v>8298</v>
       </c>
       <c r="Q183" t="n">
         <v>1</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>'+1 page unreachable (unverifiable)</t>
+        </is>
+      </c>
       <c r="T183" t="n">
         <v>0</v>
       </c>
@@ -12323,14 +12309,14 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.facebook.com</t>
+          <t>https://www.target.com</t>
         </is>
       </c>
       <c r="B184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D184" t="n">
         <v>2</v>
@@ -12360,7 +12346,7 @@
         <v>-0</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N184" t="b">
         <v>0</v>
@@ -12369,19 +12355,15 @@
         <v>0</v>
       </c>
       <c r="P184" t="n">
-        <v>10761</v>
+        <v>10847</v>
       </c>
       <c r="Q184" t="n">
         <v>1</v>
       </c>
       <c r="R184" t="n">
-        <v>1</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>'+1 page unreachable (unverifiable)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr"/>
       <c r="T184" t="n">
         <v>0</v>
       </c>
@@ -12389,14 +12371,14 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.pinterest.com</t>
+          <t>https://www.wellsfargo.com</t>
         </is>
       </c>
       <c r="B185" t="b">
         <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D185" t="n">
         <v>2</v>
@@ -12426,24 +12408,28 @@
         <v>-0</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P185" t="n">
-        <v>6135</v>
+        <v>12192</v>
       </c>
       <c r="Q185" t="n">
         <v>1</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>'+4 password field + external form (credential harvesting pattern)</t>
+        </is>
+      </c>
       <c r="T185" t="n">
         <v>0</v>
       </c>
@@ -12451,14 +12437,14 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.stackoverflow.com</t>
+          <t>https://www.facebook.com</t>
         </is>
       </c>
       <c r="B186" t="b">
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D186" t="n">
         <v>2</v>
@@ -12497,7 +12483,7 @@
         <v>0</v>
       </c>
       <c r="P186" t="n">
-        <v>8297</v>
+        <v>10761</v>
       </c>
       <c r="Q186" t="n">
         <v>1</v>
@@ -12517,7 +12503,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.wordpress.com</t>
+          <t>https://www.pinterest.com</t>
         </is>
       </c>
       <c r="B187" t="b">
@@ -12554,28 +12540,24 @@
         <v>-0</v>
       </c>
       <c r="M187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N187" t="b">
         <v>0</v>
       </c>
       <c r="O187" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P187" t="n">
-        <v>9691</v>
+        <v>6136</v>
       </c>
       <c r="Q187" t="n">
         <v>1</v>
       </c>
       <c r="R187" t="n">
-        <v>3</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>'+3 form posts to another host</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S187" t="inlineStr"/>
       <c r="T187" t="n">
         <v>0</v>
       </c>
@@ -12583,14 +12565,14 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.yahoo.com</t>
+          <t>https://www.wordpress.com</t>
         </is>
       </c>
       <c r="B188" t="b">
         <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D188" t="n">
         <v>2</v>
@@ -12626,18 +12608,22 @@
         <v>0</v>
       </c>
       <c r="O188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P188" t="n">
-        <v>11562</v>
+        <v>9691</v>
       </c>
       <c r="Q188" t="n">
         <v>1</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>'+1 form posts to another host</t>
+        </is>
+      </c>
       <c r="T188" t="n">
         <v>0</v>
       </c>
@@ -12707,17 +12693,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.aws.amazon.com</t>
+          <t>https://www.yahoo.com</t>
         </is>
       </c>
       <c r="B190" t="b">
         <v>1</v>
       </c>
       <c r="C190" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -12744,7 +12730,7 @@
         <v>-0</v>
       </c>
       <c r="M190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -12753,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>11640</v>
+        <v>11562</v>
       </c>
       <c r="Q190" t="n">
         <v>1</v>
@@ -12769,14 +12755,14 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.digitalocean.com</t>
+          <t>https://www.ibm.com</t>
         </is>
       </c>
       <c r="B191" t="b">
         <v>1</v>
       </c>
       <c r="C191" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D191" t="n">
         <v>2</v>
@@ -12806,7 +12792,7 @@
         <v>-0</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N191" t="b">
         <v>0</v>
@@ -12815,7 +12801,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="n">
-        <v>9651</v>
+        <v>14789</v>
       </c>
       <c r="Q191" t="n">
         <v>1</v>
@@ -12831,17 +12817,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.notion.so</t>
+          <t>https://www.aws.amazon.com</t>
         </is>
       </c>
       <c r="B192" t="b">
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -12868,7 +12854,7 @@
         <v>-0</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N192" t="b">
         <v>0</v>
@@ -12877,7 +12863,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="n">
-        <v>4185</v>
+        <v>11640</v>
       </c>
       <c r="Q192" t="n">
         <v>1</v>
@@ -12893,14 +12879,14 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com</t>
+          <t>https://www.digitalocean.com</t>
         </is>
       </c>
       <c r="B193" t="b">
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D193" t="n">
         <v>2</v>
@@ -12939,7 +12925,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="n">
-        <v>9310</v>
+        <v>9651</v>
       </c>
       <c r="Q193" t="n">
         <v>1</v>
@@ -13001,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="P194" t="n">
-        <v>9263</v>
+        <v>9264</v>
       </c>
       <c r="Q194" t="n">
         <v>1</v>
@@ -13017,14 +13003,14 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.figma.com</t>
+          <t>https://www.atlassian.com</t>
         </is>
       </c>
       <c r="B195" t="b">
         <v>1</v>
       </c>
       <c r="C195" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D195" t="n">
         <v>2</v>
@@ -13063,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="P195" t="n">
-        <v>10019</v>
+        <v>9310</v>
       </c>
       <c r="Q195" t="n">
         <v>1</v>
@@ -13079,14 +13065,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.trello.com</t>
+          <t>https://www.notion.so</t>
         </is>
       </c>
       <c r="B196" t="b">
         <v>1</v>
       </c>
       <c r="C196" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D196" t="n">
         <v>2</v>
@@ -13116,28 +13102,24 @@
         <v>-0</v>
       </c>
       <c r="M196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N196" t="b">
         <v>0</v>
       </c>
       <c r="O196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P196" t="n">
-        <v>8059</v>
+        <v>4185</v>
       </c>
       <c r="Q196" t="n">
         <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>3</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>'+3 form posts to another host</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr"/>
       <c r="T196" t="n">
         <v>0</v>
       </c>
@@ -13145,7 +13127,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.asana.com</t>
+          <t>https://www.figma.com</t>
         </is>
       </c>
       <c r="B197" t="b">
@@ -13182,7 +13164,7 @@
         <v>-0</v>
       </c>
       <c r="M197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N197" t="b">
         <v>0</v>
@@ -13191,7 +13173,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>6444</v>
+        <v>10019</v>
       </c>
       <c r="Q197" t="n">
         <v>1</v>
@@ -13207,14 +13189,14 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.walmart.com</t>
+          <t>https://www.trello.com</t>
         </is>
       </c>
       <c r="B198" t="b">
         <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D198" t="n">
         <v>2</v>
@@ -13244,24 +13226,28 @@
         <v>-0</v>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N198" t="b">
         <v>0</v>
       </c>
       <c r="O198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P198" t="n">
-        <v>11526</v>
+        <v>8060</v>
       </c>
       <c r="Q198" t="n">
         <v>1</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>'+1 form posts to another host</t>
+        </is>
+      </c>
       <c r="T198" t="n">
         <v>0</v>
       </c>
@@ -13269,14 +13255,14 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.bankofamerica.com</t>
+          <t>https://www.asana.com</t>
         </is>
       </c>
       <c r="B199" t="b">
         <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D199" t="n">
         <v>2</v>
@@ -13306,7 +13292,7 @@
         <v>-0</v>
       </c>
       <c r="M199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N199" t="b">
         <v>0</v>
@@ -13315,7 +13301,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>10122</v>
+        <v>6445</v>
       </c>
       <c r="Q199" t="n">
         <v>1</v>
@@ -13377,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="P200" t="n">
-        <v>9732</v>
+        <v>9733</v>
       </c>
       <c r="Q200" t="n">
         <v>1</v>
